--- a/artfynd/A 39687-2024 artfynd.xlsx
+++ b/artfynd/A 39687-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119364559</v>
+        <v>119364538</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119364538</v>
+        <v>119364763</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443509</v>
+        <v>443582</v>
       </c>
       <c r="R3" t="n">
-        <v>6932865</v>
+        <v>6933030</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +892,11 @@
         <v>119364909</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119364423</v>
+        <v>119364785</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443509</v>
+        <v>443577</v>
       </c>
       <c r="R5" t="n">
-        <v>6932865</v>
+        <v>6933028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1100,220 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119364423</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr-Veman, Norr-Veman, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>443509</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6932865</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119364559</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr-Veman, Norr-Veman, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>443509</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6932865</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39687-2024 artfynd.xlsx
+++ b/artfynd/A 39687-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119364538</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119364763</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119364909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119364785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119364423</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,8 +1344,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119364559</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>